--- a/Suite-Meter_List_Oxford.xlsx
+++ b/Suite-Meter_List_Oxford.xlsx
@@ -1,3 +1,39 @@
+
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://enerprosystems-my.sharepoint.com/personal/ehubicka_enerprosystems_com/Documents/Documents/Eric's Files (old laptop)/5.COMMISSIONING FILES/Oxford/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{50AF0651-29F4-4EE8-9784-07FC20D29DBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="30960" windowHeight="16800" xr2:uid="{1B09DD8F-904A-455C-A234-65B47F6FC387}"/>
+  </bookViews>
+  <sheets>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+  </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
+</workbook>
+</file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="5">
@@ -388,4 +424,3111 @@
     </a:ext>
   </a:extLst>
 </a:theme>
+</file>
+
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{995065FC-B0B2-4267-B22B-36E648AD012A}">
+  <dimension ref="A1:C281"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>101</v>
+      </c>
+      <c r="B2" s="1">
+        <v>24023126</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>101</v>
+      </c>
+      <c r="B3" s="1">
+        <v>24064186</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>102</v>
+      </c>
+      <c r="B4" s="1">
+        <v>24064176</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>102</v>
+      </c>
+      <c r="B5" s="1">
+        <v>24064169</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>103</v>
+      </c>
+      <c r="B6" s="1">
+        <v>24064171</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>103</v>
+      </c>
+      <c r="B7" s="1">
+        <v>24064180</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>104</v>
+      </c>
+      <c r="B8" s="1">
+        <v>24064179</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>104</v>
+      </c>
+      <c r="B9" s="1">
+        <v>24064184</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>105</v>
+      </c>
+      <c r="B10" s="1">
+        <v>24064177</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>105</v>
+      </c>
+      <c r="B11" s="1">
+        <v>24064170</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>106</v>
+      </c>
+      <c r="B12" s="1">
+        <v>24064174</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>106</v>
+      </c>
+      <c r="B13" s="1">
+        <v>24064172</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>107</v>
+      </c>
+      <c r="B14" s="1">
+        <v>24064182</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>107</v>
+      </c>
+      <c r="B15" s="1">
+        <v>24064183</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>108</v>
+      </c>
+      <c r="B16" s="1">
+        <v>24064199</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>108</v>
+      </c>
+      <c r="B17" s="1">
+        <v>24064181</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>109</v>
+      </c>
+      <c r="B18" s="1">
+        <v>24064188</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>109</v>
+      </c>
+      <c r="B19" s="1">
+        <v>24064193</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>110</v>
+      </c>
+      <c r="B20" s="1">
+        <v>24064191</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>110</v>
+      </c>
+      <c r="B21" s="1">
+        <v>24064198</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>111</v>
+      </c>
+      <c r="B22" s="1">
+        <v>24064195</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>111</v>
+      </c>
+      <c r="B23" s="1">
+        <v>24064197</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>112</v>
+      </c>
+      <c r="B24" s="1">
+        <v>24064185</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>112</v>
+      </c>
+      <c r="B25" s="1">
+        <v>24064196</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>113</v>
+      </c>
+      <c r="B26" s="1">
+        <v>24064200</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>113</v>
+      </c>
+      <c r="B27" s="1">
+        <v>24064194</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>114</v>
+      </c>
+      <c r="B28" s="1">
+        <v>24064187</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>114</v>
+      </c>
+      <c r="B29" s="1">
+        <v>24064178</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>115</v>
+      </c>
+      <c r="B30" s="1">
+        <v>24064189</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>115</v>
+      </c>
+      <c r="B31" s="1">
+        <v>24064190</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>201</v>
+      </c>
+      <c r="B32" s="1">
+        <v>24063640</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>201</v>
+      </c>
+      <c r="B33" s="1">
+        <v>24063616</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>202</v>
+      </c>
+      <c r="B34" s="1">
+        <v>24024835</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
+        <v>202</v>
+      </c>
+      <c r="B35" s="1">
+        <v>24063650</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>203</v>
+      </c>
+      <c r="B36" s="1">
+        <v>24064161</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
+        <v>203</v>
+      </c>
+      <c r="B37" s="1">
+        <v>24064173</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>204</v>
+      </c>
+      <c r="B38" s="1">
+        <v>24064163</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
+        <v>204</v>
+      </c>
+      <c r="B39" s="1">
+        <v>24064151</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
+        <v>205</v>
+      </c>
+      <c r="B40" s="1">
+        <v>24064162</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
+        <v>205</v>
+      </c>
+      <c r="B41" s="1">
+        <v>24064159</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
+        <v>206</v>
+      </c>
+      <c r="B42" s="1">
+        <v>24064175</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
+        <v>206</v>
+      </c>
+      <c r="B43" s="1">
+        <v>24064168</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
+        <v>207</v>
+      </c>
+      <c r="B44" s="1">
+        <v>24023147</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
+        <v>207</v>
+      </c>
+      <c r="B45" s="1">
+        <v>24023142</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
+        <v>208</v>
+      </c>
+      <c r="B46" s="1">
+        <v>24064158</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
+        <v>208</v>
+      </c>
+      <c r="B47" s="1">
+        <v>24064167</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
+        <v>209</v>
+      </c>
+      <c r="B48" s="1">
+        <v>24064165</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
+        <v>209</v>
+      </c>
+      <c r="B49" s="1">
+        <v>24064166</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
+        <v>210</v>
+      </c>
+      <c r="B50" s="1">
+        <v>24023138</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
+        <v>210</v>
+      </c>
+      <c r="B51" s="1">
+        <v>24023133</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
+        <v>211</v>
+      </c>
+      <c r="B52" s="1">
+        <v>24023139</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
+        <v>211</v>
+      </c>
+      <c r="B53" s="1">
+        <v>24023140</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
+        <v>212</v>
+      </c>
+      <c r="B54" s="1">
+        <v>24063613</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
+        <v>212</v>
+      </c>
+      <c r="B55" s="1">
+        <v>24063628</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
+        <v>213</v>
+      </c>
+      <c r="B56" s="1">
+        <v>24063642</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
+        <v>213</v>
+      </c>
+      <c r="B57" s="1">
+        <v>24063643</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
+        <v>214</v>
+      </c>
+      <c r="B58" s="1">
+        <v>25017928</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="1">
+        <v>214</v>
+      </c>
+      <c r="B59" s="1">
+        <v>24063649</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="1">
+        <v>215</v>
+      </c>
+      <c r="B60" s="1">
+        <v>24063632</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
+        <v>215</v>
+      </c>
+      <c r="B61" s="1">
+        <v>24063623</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="1">
+        <v>216</v>
+      </c>
+      <c r="B62" s="1">
+        <v>24024818</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="1">
+        <v>216</v>
+      </c>
+      <c r="B63" s="1">
+        <v>24024817</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="1">
+        <v>217</v>
+      </c>
+      <c r="B64" s="1">
+        <v>25017947</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="1">
+        <v>217</v>
+      </c>
+      <c r="B65" s="1">
+        <v>24063635</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="1">
+        <v>218</v>
+      </c>
+      <c r="B66" s="1">
+        <v>24024822</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="1">
+        <v>218</v>
+      </c>
+      <c r="B67" s="1">
+        <v>24024820</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="1">
+        <v>219</v>
+      </c>
+      <c r="B68" s="1">
+        <v>24024829</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="1">
+        <v>219</v>
+      </c>
+      <c r="B69" s="1">
+        <v>24063636</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="1">
+        <v>220</v>
+      </c>
+      <c r="B70" s="1">
+        <v>25017903</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="1">
+        <v>220</v>
+      </c>
+      <c r="B71" s="1">
+        <v>24063639</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="1">
+        <v>221</v>
+      </c>
+      <c r="B72" s="1">
+        <v>25017916</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="1">
+        <v>221</v>
+      </c>
+      <c r="B73" s="1">
+        <v>24063648</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="1">
+        <v>222</v>
+      </c>
+      <c r="B74" s="1">
+        <v>24024819</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="1">
+        <v>222</v>
+      </c>
+      <c r="B75" s="1">
+        <v>24024826</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="1">
+        <v>223</v>
+      </c>
+      <c r="B76" s="1">
+        <v>24024831</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="1">
+        <v>223</v>
+      </c>
+      <c r="B77" s="1">
+        <v>24024825</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="1">
+        <v>224</v>
+      </c>
+      <c r="B78" s="1">
+        <v>24063617</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="1">
+        <v>224</v>
+      </c>
+      <c r="B79" s="1">
+        <v>24063621</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="1">
+        <v>225</v>
+      </c>
+      <c r="B80" s="1">
+        <v>25017910</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="1">
+        <v>225</v>
+      </c>
+      <c r="B81" s="1">
+        <v>24063625</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="1">
+        <v>301</v>
+      </c>
+      <c r="B82" s="1">
+        <v>24024844</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="1">
+        <v>301</v>
+      </c>
+      <c r="B83" s="1">
+        <v>24024843</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="1">
+        <v>302</v>
+      </c>
+      <c r="B84" s="1">
+        <v>24024839</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="1">
+        <v>302</v>
+      </c>
+      <c r="B85" s="1">
+        <v>24024842</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="1">
+        <v>303</v>
+      </c>
+      <c r="B86" s="1">
+        <v>24024840</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="1">
+        <v>303</v>
+      </c>
+      <c r="B87" s="1">
+        <v>24024833</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="1">
+        <v>304</v>
+      </c>
+      <c r="B88" s="1">
+        <v>24024845</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="1">
+        <v>304</v>
+      </c>
+      <c r="B89" s="1">
+        <v>24024847</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="1">
+        <v>305</v>
+      </c>
+      <c r="B90" s="1">
+        <v>24063646</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="1">
+        <v>305</v>
+      </c>
+      <c r="B91" s="1">
+        <v>24063645</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="1">
+        <v>306</v>
+      </c>
+      <c r="B92" s="1">
+        <v>24024841</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="1">
+        <v>306</v>
+      </c>
+      <c r="B93" s="1">
+        <v>24024848</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="1">
+        <v>307</v>
+      </c>
+      <c r="B94" s="1">
+        <v>24024838</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="1">
+        <v>307</v>
+      </c>
+      <c r="B95" s="1">
+        <v>24063647</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="1">
+        <v>308</v>
+      </c>
+      <c r="B96" s="1">
+        <v>25017924</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="1">
+        <v>308</v>
+      </c>
+      <c r="B97" s="1">
+        <v>24025226</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="1">
+        <v>309</v>
+      </c>
+      <c r="B98" s="1">
+        <v>24024832</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="1">
+        <v>309</v>
+      </c>
+      <c r="B99" s="1">
+        <v>24024836</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="1">
+        <v>310</v>
+      </c>
+      <c r="B100" s="1">
+        <v>24024837</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="1">
+        <v>310</v>
+      </c>
+      <c r="B101" s="1">
+        <v>24024846</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="1">
+        <v>311</v>
+      </c>
+      <c r="B102" s="1">
+        <v>24024850</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="1">
+        <v>311</v>
+      </c>
+      <c r="B103" s="1">
+        <v>24024849</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="1">
+        <v>312</v>
+      </c>
+      <c r="B104" s="1">
+        <v>25017902</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" s="1">
+        <v>312</v>
+      </c>
+      <c r="B105" s="1">
+        <v>25017949</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" s="1">
+        <v>313</v>
+      </c>
+      <c r="B106" s="1">
+        <v>24024824</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="1">
+        <v>313</v>
+      </c>
+      <c r="B107" s="1">
+        <v>25017937</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" s="1">
+        <v>314</v>
+      </c>
+      <c r="B108" s="1">
+        <v>24024827</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" s="1">
+        <v>314</v>
+      </c>
+      <c r="B109" s="1">
+        <v>25017939</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" s="1">
+        <v>315</v>
+      </c>
+      <c r="B110" s="1">
+        <v>24024828</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" s="1">
+        <v>315</v>
+      </c>
+      <c r="B111" s="1">
+        <v>24024814</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" s="1">
+        <v>316</v>
+      </c>
+      <c r="B112" s="1">
+        <v>24024816</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" s="1">
+        <v>316</v>
+      </c>
+      <c r="B113" s="1">
+        <v>24024813</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" s="1">
+        <v>317</v>
+      </c>
+      <c r="B114" s="1">
+        <v>24024807</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" s="1">
+        <v>317</v>
+      </c>
+      <c r="B115" s="1">
+        <v>24024810</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" s="1">
+        <v>318</v>
+      </c>
+      <c r="B116" s="1">
+        <v>24024801</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" s="1">
+        <v>318</v>
+      </c>
+      <c r="B117" s="1">
+        <v>24024811</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" s="1">
+        <v>319</v>
+      </c>
+      <c r="B118" s="1">
+        <v>24024809</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" s="1">
+        <v>319</v>
+      </c>
+      <c r="B119" s="1">
+        <v>24024804</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" s="1">
+        <v>320</v>
+      </c>
+      <c r="B120" s="1">
+        <v>24024815</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" s="1">
+        <v>320</v>
+      </c>
+      <c r="B121" s="1">
+        <v>24024803</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" s="1">
+        <v>321</v>
+      </c>
+      <c r="B122" s="1">
+        <v>24024802</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" s="1">
+        <v>321</v>
+      </c>
+      <c r="B123" s="1">
+        <v>24024808</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" s="1">
+        <v>322</v>
+      </c>
+      <c r="B124" s="1">
+        <v>24024806</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" s="1">
+        <v>322</v>
+      </c>
+      <c r="B125" s="1">
+        <v>24024805</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" s="1">
+        <v>323</v>
+      </c>
+      <c r="B126" s="1">
+        <v>24024821</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" s="1">
+        <v>323</v>
+      </c>
+      <c r="B127" s="1">
+        <v>24024812</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" s="1">
+        <v>324</v>
+      </c>
+      <c r="B128" s="1">
+        <v>24024823</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" s="1">
+        <v>324</v>
+      </c>
+      <c r="B129" s="1">
+        <v>24024834</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" s="1">
+        <v>325</v>
+      </c>
+      <c r="B130" s="1">
+        <v>24063624</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" s="1">
+        <v>325</v>
+      </c>
+      <c r="B131" s="1">
+        <v>24024830</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" s="1">
+        <v>401</v>
+      </c>
+      <c r="B132" s="1">
+        <v>25017909</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" s="1">
+        <v>401</v>
+      </c>
+      <c r="B133" s="1">
+        <v>24063637</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" s="1">
+        <v>402</v>
+      </c>
+      <c r="B134" s="1">
+        <v>25017944</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" s="1">
+        <v>402</v>
+      </c>
+      <c r="B135" s="1">
+        <v>24063620</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" s="1">
+        <v>403</v>
+      </c>
+      <c r="B136" s="1">
+        <v>25017945</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" s="1">
+        <v>403</v>
+      </c>
+      <c r="B137" s="1">
+        <v>25017932</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" s="1">
+        <v>404</v>
+      </c>
+      <c r="B138" s="1">
+        <v>25017911</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" s="1">
+        <v>404</v>
+      </c>
+      <c r="B139" s="1">
+        <v>24063630</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" s="1">
+        <v>405</v>
+      </c>
+      <c r="B140" s="1">
+        <v>25017946</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" s="1">
+        <v>405</v>
+      </c>
+      <c r="B141" s="1">
+        <v>25017907</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" s="1">
+        <v>406</v>
+      </c>
+      <c r="B142" s="1">
+        <v>25017934</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" s="1">
+        <v>406</v>
+      </c>
+      <c r="B143" s="1">
+        <v>25017917</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" s="1">
+        <v>407</v>
+      </c>
+      <c r="B144" s="1">
+        <v>25017908</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" s="1">
+        <v>407</v>
+      </c>
+      <c r="B145" s="1">
+        <v>25017913</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" s="1">
+        <v>408</v>
+      </c>
+      <c r="B146" s="1">
+        <v>25017925</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" s="1">
+        <v>408</v>
+      </c>
+      <c r="B147" s="1">
+        <v>25017943</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" s="1">
+        <v>409</v>
+      </c>
+      <c r="B148" s="1">
+        <v>25017936</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" s="1">
+        <v>409</v>
+      </c>
+      <c r="B149" s="1">
+        <v>25017905</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" s="1">
+        <v>410</v>
+      </c>
+      <c r="B150" s="1">
+        <v>25017919</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" s="1">
+        <v>410</v>
+      </c>
+      <c r="B151" s="1">
+        <v>25017904</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" s="1">
+        <v>411</v>
+      </c>
+      <c r="B152" s="1">
+        <v>25017948</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" s="1">
+        <v>411</v>
+      </c>
+      <c r="B153" s="1">
+        <v>25017942</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" s="1">
+        <v>412</v>
+      </c>
+      <c r="B154" s="1">
+        <v>25017912</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" s="1">
+        <v>412</v>
+      </c>
+      <c r="B155" s="1">
+        <v>25017922</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" s="1">
+        <v>413</v>
+      </c>
+      <c r="B156" s="1">
+        <v>24063641</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" s="1">
+        <v>413</v>
+      </c>
+      <c r="B157" s="1">
+        <v>25017915</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" s="1">
+        <v>414</v>
+      </c>
+      <c r="B158" s="1">
+        <v>24063627</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" s="1">
+        <v>414</v>
+      </c>
+      <c r="B159" s="1">
+        <v>24025201</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" s="1">
+        <v>415</v>
+      </c>
+      <c r="B160" s="1">
+        <v>25017930</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" s="1">
+        <v>415</v>
+      </c>
+      <c r="B161" s="1">
+        <v>24063631</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162" s="1">
+        <v>416</v>
+      </c>
+      <c r="B162" s="1">
+        <v>25017933</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" s="1">
+        <v>416</v>
+      </c>
+      <c r="B163" s="1">
+        <v>25017926</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" s="1">
+        <v>417</v>
+      </c>
+      <c r="B164" s="1">
+        <v>25017923</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165" s="1">
+        <v>417</v>
+      </c>
+      <c r="B165" s="1">
+        <v>25017929</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" s="1">
+        <v>418</v>
+      </c>
+      <c r="B166" s="1">
+        <v>25017901</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" s="1">
+        <v>418</v>
+      </c>
+      <c r="B167" s="1">
+        <v>25017906</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168" s="1">
+        <v>419</v>
+      </c>
+      <c r="B168" s="1">
+        <v>25017938</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" s="1">
+        <v>419</v>
+      </c>
+      <c r="B169" s="1">
+        <v>25017935</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170" s="1">
+        <v>420</v>
+      </c>
+      <c r="B170" s="1">
+        <v>25017950</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171" s="1">
+        <v>420</v>
+      </c>
+      <c r="B171" s="1">
+        <v>25017940</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172" s="1">
+        <v>421</v>
+      </c>
+      <c r="B172" s="1">
+        <v>24063618</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173" s="1">
+        <v>421</v>
+      </c>
+      <c r="B173" s="1">
+        <v>24063633</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174" s="1">
+        <v>422</v>
+      </c>
+      <c r="B174" s="1">
+        <v>25017931</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175" s="1">
+        <v>422</v>
+      </c>
+      <c r="B175" s="1">
+        <v>25017941</v>
+      </c>
+      <c r="C175" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176" s="1">
+        <v>423</v>
+      </c>
+      <c r="B176" s="1">
+        <v>25017914</v>
+      </c>
+      <c r="C176" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177" s="1">
+        <v>423</v>
+      </c>
+      <c r="B177" s="1">
+        <v>25017927</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" s="1">
+        <v>424</v>
+      </c>
+      <c r="B178" s="1">
+        <v>24063629</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" s="1">
+        <v>424</v>
+      </c>
+      <c r="B179" s="1">
+        <v>25017918</v>
+      </c>
+      <c r="C179" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" s="1">
+        <v>425</v>
+      </c>
+      <c r="B180" s="1">
+        <v>25017920</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" s="1">
+        <v>425</v>
+      </c>
+      <c r="B181" s="1">
+        <v>25017921</v>
+      </c>
+      <c r="C181" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" s="1">
+        <v>501</v>
+      </c>
+      <c r="B182" s="1">
+        <v>25017832</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183" s="1">
+        <v>501</v>
+      </c>
+      <c r="B183" s="1">
+        <v>25017811</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184" s="1">
+        <v>502</v>
+      </c>
+      <c r="B184" s="1">
+        <v>25017828</v>
+      </c>
+      <c r="C184" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185" s="1">
+        <v>502</v>
+      </c>
+      <c r="B185" s="1">
+        <v>25017830</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A186" s="1">
+        <v>503</v>
+      </c>
+      <c r="B186" s="1">
+        <v>25017816</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187" s="1">
+        <v>503</v>
+      </c>
+      <c r="B187" s="1">
+        <v>25017810</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188" s="1">
+        <v>504</v>
+      </c>
+      <c r="B188" s="1">
+        <v>25017839</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A189" s="1">
+        <v>504</v>
+      </c>
+      <c r="B189" s="1">
+        <v>25017803</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190" s="1">
+        <v>505</v>
+      </c>
+      <c r="B190" s="1">
+        <v>25017826</v>
+      </c>
+      <c r="C190" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191" s="1">
+        <v>505</v>
+      </c>
+      <c r="B191" s="1">
+        <v>25017817</v>
+      </c>
+      <c r="C191" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192" s="1">
+        <v>506</v>
+      </c>
+      <c r="B192" s="1">
+        <v>25017819</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" s="1">
+        <v>506</v>
+      </c>
+      <c r="B193" s="1">
+        <v>25017825</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194" s="1">
+        <v>507</v>
+      </c>
+      <c r="B194" s="1">
+        <v>25017824</v>
+      </c>
+      <c r="C194" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195" s="1">
+        <v>507</v>
+      </c>
+      <c r="B195" s="1">
+        <v>25017822</v>
+      </c>
+      <c r="C195" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196" s="1">
+        <v>508</v>
+      </c>
+      <c r="B196" s="1">
+        <v>25017829</v>
+      </c>
+      <c r="C196" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197" s="1">
+        <v>508</v>
+      </c>
+      <c r="B197" s="1">
+        <v>25017821</v>
+      </c>
+      <c r="C197" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198" s="1">
+        <v>509</v>
+      </c>
+      <c r="B198" s="1">
+        <v>25017848</v>
+      </c>
+      <c r="C198" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199" s="1">
+        <v>509</v>
+      </c>
+      <c r="B199" s="1">
+        <v>25017835</v>
+      </c>
+      <c r="C199" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200" s="1">
+        <v>510</v>
+      </c>
+      <c r="B200" s="1">
+        <v>25017850</v>
+      </c>
+      <c r="C200" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A201" s="1">
+        <v>510</v>
+      </c>
+      <c r="B201" s="1">
+        <v>25017827</v>
+      </c>
+      <c r="C201" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202" s="1">
+        <v>511</v>
+      </c>
+      <c r="B202" s="1">
+        <v>25017834</v>
+      </c>
+      <c r="C202" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203" s="1">
+        <v>511</v>
+      </c>
+      <c r="B203" s="1">
+        <v>25017836</v>
+      </c>
+      <c r="C203" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A204" s="1">
+        <v>512</v>
+      </c>
+      <c r="B204" s="1">
+        <v>24023132</v>
+      </c>
+      <c r="C204" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205" s="1">
+        <v>512</v>
+      </c>
+      <c r="B205" s="1">
+        <v>24064192</v>
+      </c>
+      <c r="C205" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206" s="1">
+        <v>513</v>
+      </c>
+      <c r="B206" s="1">
+        <v>25017841</v>
+      </c>
+      <c r="C206" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A207" s="1">
+        <v>513</v>
+      </c>
+      <c r="B207" s="1">
+        <v>25017840</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208" s="1">
+        <v>514</v>
+      </c>
+      <c r="B208" s="1">
+        <v>25017838</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" s="1">
+        <v>514</v>
+      </c>
+      <c r="B209" s="1">
+        <v>25017805</v>
+      </c>
+      <c r="C209" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A210" s="1">
+        <v>515</v>
+      </c>
+      <c r="B210" s="1">
+        <v>25017849</v>
+      </c>
+      <c r="C210" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211" s="1">
+        <v>515</v>
+      </c>
+      <c r="B211" s="1">
+        <v>25017837</v>
+      </c>
+      <c r="C211" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212" s="1">
+        <v>516</v>
+      </c>
+      <c r="B212" s="1">
+        <v>25017842</v>
+      </c>
+      <c r="C212" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A213" s="1">
+        <v>516</v>
+      </c>
+      <c r="B213" s="1">
+        <v>25017845</v>
+      </c>
+      <c r="C213" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214" s="1">
+        <v>517</v>
+      </c>
+      <c r="B214" s="1">
+        <v>25017815</v>
+      </c>
+      <c r="C214" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215" s="1">
+        <v>517</v>
+      </c>
+      <c r="B215" s="1">
+        <v>25017820</v>
+      </c>
+      <c r="C215" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A216" s="1">
+        <v>518</v>
+      </c>
+      <c r="B216" s="1">
+        <v>25017813</v>
+      </c>
+      <c r="C216" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A217" s="1">
+        <v>518</v>
+      </c>
+      <c r="B217" s="1">
+        <v>25017801</v>
+      </c>
+      <c r="C217" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A218" s="1">
+        <v>519</v>
+      </c>
+      <c r="B218" s="1">
+        <v>25017804</v>
+      </c>
+      <c r="C218" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A219" s="1">
+        <v>519</v>
+      </c>
+      <c r="B219" s="1">
+        <v>25017808</v>
+      </c>
+      <c r="C219" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A220" s="1">
+        <v>520</v>
+      </c>
+      <c r="B220" s="1">
+        <v>25017802</v>
+      </c>
+      <c r="C220" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A221" s="1">
+        <v>520</v>
+      </c>
+      <c r="B221" s="1">
+        <v>25017843</v>
+      </c>
+      <c r="C221" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A222" s="1">
+        <v>521</v>
+      </c>
+      <c r="B222" s="1">
+        <v>25017833</v>
+      </c>
+      <c r="C222" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A223" s="1">
+        <v>521</v>
+      </c>
+      <c r="B223" s="1">
+        <v>25017844</v>
+      </c>
+      <c r="C223" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A224" s="1">
+        <v>522</v>
+      </c>
+      <c r="B224" s="1">
+        <v>25017846</v>
+      </c>
+      <c r="C224" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A225" s="1">
+        <v>522</v>
+      </c>
+      <c r="B225" s="1">
+        <v>25017831</v>
+      </c>
+      <c r="C225" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A226" s="1">
+        <v>523</v>
+      </c>
+      <c r="B226" s="1">
+        <v>25017807</v>
+      </c>
+      <c r="C226" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A227" s="1">
+        <v>523</v>
+      </c>
+      <c r="B227" s="1">
+        <v>25017823</v>
+      </c>
+      <c r="C227" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A228" s="1">
+        <v>524</v>
+      </c>
+      <c r="B228" s="1">
+        <v>24063638</v>
+      </c>
+      <c r="C228" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A229" s="1">
+        <v>524</v>
+      </c>
+      <c r="B229" s="1">
+        <v>24063634</v>
+      </c>
+      <c r="C229" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A230" s="1">
+        <v>525</v>
+      </c>
+      <c r="B230" s="1">
+        <v>24063626</v>
+      </c>
+      <c r="C230" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A231" s="1">
+        <v>525</v>
+      </c>
+      <c r="B231" s="1">
+        <v>24063644</v>
+      </c>
+      <c r="C231" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A232" s="1">
+        <v>601</v>
+      </c>
+      <c r="B232" s="1">
+        <v>25016269</v>
+      </c>
+      <c r="C232" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A233" s="1">
+        <v>601</v>
+      </c>
+      <c r="B233" s="1">
+        <v>25016267</v>
+      </c>
+      <c r="C233" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A234" s="1">
+        <v>602</v>
+      </c>
+      <c r="B234" s="1">
+        <v>25016292</v>
+      </c>
+      <c r="C234" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A235" s="1">
+        <v>602</v>
+      </c>
+      <c r="B235" s="1">
+        <v>25016293</v>
+      </c>
+      <c r="C235" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A236" s="1">
+        <v>603</v>
+      </c>
+      <c r="B236" s="1">
+        <v>25016265</v>
+      </c>
+      <c r="C236" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A237" s="1">
+        <v>603</v>
+      </c>
+      <c r="B237" s="1">
+        <v>25016281</v>
+      </c>
+      <c r="C237" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A238" s="1">
+        <v>604</v>
+      </c>
+      <c r="B238" s="1">
+        <v>25016277</v>
+      </c>
+      <c r="C238" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A239" s="1">
+        <v>604</v>
+      </c>
+      <c r="B239" s="1">
+        <v>25016287</v>
+      </c>
+      <c r="C239" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A240" s="1">
+        <v>605</v>
+      </c>
+      <c r="B240" s="1">
+        <v>25016286</v>
+      </c>
+      <c r="C240" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A241" s="1">
+        <v>605</v>
+      </c>
+      <c r="B241" s="1">
+        <v>25016276</v>
+      </c>
+      <c r="C241" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A242" s="1">
+        <v>606</v>
+      </c>
+      <c r="B242" s="1">
+        <v>25016291</v>
+      </c>
+      <c r="C242" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A243" s="1">
+        <v>606</v>
+      </c>
+      <c r="B243" s="1">
+        <v>25016289</v>
+      </c>
+      <c r="C243" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A244" s="1">
+        <v>607</v>
+      </c>
+      <c r="B244" s="1">
+        <v>25016275</v>
+      </c>
+      <c r="C244" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A245" s="1">
+        <v>607</v>
+      </c>
+      <c r="B245" s="1">
+        <v>25016285</v>
+      </c>
+      <c r="C245" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A246" s="1">
+        <v>608</v>
+      </c>
+      <c r="B246" s="1">
+        <v>25016295</v>
+      </c>
+      <c r="C246" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A247" s="1">
+        <v>608</v>
+      </c>
+      <c r="B247" s="1">
+        <v>25016296</v>
+      </c>
+      <c r="C247" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A248" s="1">
+        <v>609</v>
+      </c>
+      <c r="B248" s="1">
+        <v>25016261</v>
+      </c>
+      <c r="C248" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A249" s="1">
+        <v>609</v>
+      </c>
+      <c r="B249" s="1">
+        <v>25016270</v>
+      </c>
+      <c r="C249" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A250" s="1">
+        <v>610</v>
+      </c>
+      <c r="B250" s="1">
+        <v>25016299</v>
+      </c>
+      <c r="C250" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A251" s="1">
+        <v>610</v>
+      </c>
+      <c r="B251" s="1">
+        <v>25016297</v>
+      </c>
+      <c r="C251" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A252" s="1">
+        <v>611</v>
+      </c>
+      <c r="B252" s="1">
+        <v>25016278</v>
+      </c>
+      <c r="C252" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A253" s="1">
+        <v>611</v>
+      </c>
+      <c r="B253" s="1">
+        <v>25016279</v>
+      </c>
+      <c r="C253" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A254" s="1">
+        <v>612</v>
+      </c>
+      <c r="B254" s="1">
+        <v>25016288</v>
+      </c>
+      <c r="C254" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A255" s="1">
+        <v>612</v>
+      </c>
+      <c r="B255" s="1">
+        <v>25016298</v>
+      </c>
+      <c r="C255" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A256" s="1">
+        <v>613</v>
+      </c>
+      <c r="B256" s="1">
+        <v>25016259</v>
+      </c>
+      <c r="C256" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A257" s="1">
+        <v>613</v>
+      </c>
+      <c r="B257" s="1">
+        <v>25016273</v>
+      </c>
+      <c r="C257" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A258" s="1">
+        <v>614</v>
+      </c>
+      <c r="B258" s="1">
+        <v>25016272</v>
+      </c>
+      <c r="C258" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A259" s="1">
+        <v>614</v>
+      </c>
+      <c r="B259" s="1">
+        <v>25016257</v>
+      </c>
+      <c r="C259" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A260" s="1">
+        <v>615</v>
+      </c>
+      <c r="B260" s="1">
+        <v>25016254</v>
+      </c>
+      <c r="C260" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A261" s="1">
+        <v>615</v>
+      </c>
+      <c r="B261" s="1">
+        <v>25016274</v>
+      </c>
+      <c r="C261" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A262" s="1">
+        <v>616</v>
+      </c>
+      <c r="B262" s="1">
+        <v>25016300</v>
+      </c>
+      <c r="C262" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A263" s="1">
+        <v>616</v>
+      </c>
+      <c r="B263" s="1">
+        <v>25016283</v>
+      </c>
+      <c r="C263" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A264" s="1">
+        <v>617</v>
+      </c>
+      <c r="B264" s="1">
+        <v>25016266</v>
+      </c>
+      <c r="C264" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A265" s="1">
+        <v>617</v>
+      </c>
+      <c r="B265" s="1">
+        <v>25016294</v>
+      </c>
+      <c r="C265" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A266" s="1">
+        <v>618</v>
+      </c>
+      <c r="B266" s="1">
+        <v>25016260</v>
+      </c>
+      <c r="C266" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A267" s="1">
+        <v>618</v>
+      </c>
+      <c r="B267" s="1">
+        <v>25016271</v>
+      </c>
+      <c r="C267" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A268" s="1">
+        <v>619</v>
+      </c>
+      <c r="B268" s="1">
+        <v>25016284</v>
+      </c>
+      <c r="C268" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A269" s="1">
+        <v>619</v>
+      </c>
+      <c r="B269" s="1">
+        <v>25016268</v>
+      </c>
+      <c r="C269" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A270" s="1">
+        <v>620</v>
+      </c>
+      <c r="B270" s="1">
+        <v>25016264</v>
+      </c>
+      <c r="C270" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A271" s="1">
+        <v>620</v>
+      </c>
+      <c r="B271" s="1">
+        <v>25016262</v>
+      </c>
+      <c r="C271" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A272" s="1">
+        <v>621</v>
+      </c>
+      <c r="B272" s="1">
+        <v>25016253</v>
+      </c>
+      <c r="C272" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A273" s="1">
+        <v>621</v>
+      </c>
+      <c r="B273" s="1">
+        <v>25016255</v>
+      </c>
+      <c r="C273" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A274" s="1">
+        <v>622</v>
+      </c>
+      <c r="B274" s="1">
+        <v>25016256</v>
+      </c>
+      <c r="C274" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A275" s="1">
+        <v>622</v>
+      </c>
+      <c r="B275" s="1">
+        <v>25016252</v>
+      </c>
+      <c r="C275" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A276" s="1">
+        <v>623</v>
+      </c>
+      <c r="B276" s="1">
+        <v>25016251</v>
+      </c>
+      <c r="C276" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A277" s="1">
+        <v>623</v>
+      </c>
+      <c r="B277" s="1">
+        <v>25016282</v>
+      </c>
+      <c r="C277" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A278" s="1">
+        <v>624</v>
+      </c>
+      <c r="B278" s="1">
+        <v>25016258</v>
+      </c>
+      <c r="C278" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A279" s="1">
+        <v>624</v>
+      </c>
+      <c r="B279" s="1">
+        <v>25016280</v>
+      </c>
+      <c r="C279" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A280" s="1">
+        <v>625</v>
+      </c>
+      <c r="B280" s="1">
+        <v>25016263</v>
+      </c>
+      <c r="C280" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A281" s="1">
+        <v>625</v>
+      </c>
+      <c r="B281" s="1">
+        <v>25016290</v>
+      </c>
+      <c r="C281" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>